--- a/Theta Scripts/lfpPropsTab.xlsx
+++ b/Theta Scripts/lfpPropsTab.xlsx
@@ -1,19 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lasss\Documents\Research\Brewer Lab work\Code\Lassers_Spike_LFP\Theta Scripts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6324C46-B546-4696-9DED-4AB096388F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="374" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="38">
   <si>
     <t>fi</t>
   </si>
@@ -132,8 +152,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -147,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -155,1404 +175,2687 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$2:$H$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="38"/>
+                <c:pt idx="0">
+                  <c:v>1.4288131797136643</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.2761927794349379</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0608676332534051</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.7048852615751064</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.7400715988091653</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0730190227354131</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.67809762510765048</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2701243163613307</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.6233705176133917</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.3165451656434648</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.097439449433935</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.76051641723572894</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1785115885130653</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.7711734733880706</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.7489436674727721</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>25.354858300166018</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3305507789801547</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.9487353224459802</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.4868752859271446</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.2812881590253946</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7.8318318047073605</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.6813176867386692</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>29.044991658266888</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>20.498144518934389</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.6581654358595261</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>83.217832380615732</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>25.742837255264842</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.1532850350478183</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.3847007284654338</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.3099572274973212</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4.1689622771732058</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>60.554468053821289</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.8854589130358157</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.4318774340669977</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.5615443852636872</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.6106555844012345</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.1085935052157296</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>15.437646991073336</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-610A-4D57-9843-8E3DC7719080}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1368860240"/>
+        <c:axId val="1368228192"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1368860240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1368228192"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1368228192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1368860240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>534670</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>96520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>227330</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>96520</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3598891-E20C-7A5D-E275-2A55B288EF75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K40"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="true"/>
-    <col min="2" max="2" width="9.26953125" customWidth="true"/>
-    <col min="3" max="3" width="8.26953125" customWidth="true"/>
-    <col min="4" max="4" width="8.7265625" customWidth="true"/>
-    <col min="5" max="5" width="5.7265625" customWidth="true"/>
-    <col min="6" max="6" width="4.36328125" customWidth="true"/>
-    <col min="7" max="7" width="12.453125" customWidth="true"/>
-    <col min="8" max="8" width="15.54296875" customWidth="true"/>
-    <col min="9" max="9" width="12.453125" customWidth="true"/>
-    <col min="10" max="10" width="19.26953125" customWidth="true"/>
-    <col min="11" max="11" width="14.81640625" customWidth="true"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="9.26953125" customWidth="1"/>
+    <col min="3" max="3" width="8.26953125" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" customWidth="1"/>
+    <col min="5" max="5" width="5.7265625" customWidth="1"/>
+    <col min="6" max="6" width="4.36328125" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" customWidth="1"/>
+    <col min="8" max="8" width="15.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" customWidth="1"/>
+    <col min="11" max="11" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="0">
-        <v>3</v>
-      </c>
-      <c r="G2" s="0">
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
         <v>1.2465909413126808</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>1.4288131797136643</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>1.0382052342031516</v>
       </c>
-      <c r="J2" s="0">
+      <c r="J2">
         <v>10.205666666666668</v>
       </c>
-      <c r="K2" s="0">
+      <c r="K2">
         <v>1.6873333333333334</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="0">
-        <v>3</v>
-      </c>
-      <c r="G3" s="0">
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
         <v>5.8070458432002932</v>
       </c>
-      <c r="H3" s="0">
+      <c r="H3">
         <v>4.2761927794349379</v>
       </c>
-      <c r="I3" s="0">
+      <c r="I3">
         <v>7.0363347265439211</v>
       </c>
-      <c r="J3" s="0">
+      <c r="J3">
         <v>7.1650000000000009</v>
       </c>
-      <c r="K3" s="0">
+      <c r="K3">
         <v>19.038</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0">
-        <v>3</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="0">
-        <v>4</v>
-      </c>
-      <c r="G4" s="0">
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
         <v>0.90047801992546339</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4">
         <v>1.0608676332534051</v>
       </c>
-      <c r="I4" s="0">
+      <c r="I4">
         <v>0.70951703206939032</v>
       </c>
-      <c r="J4" s="0">
+      <c r="J4">
         <v>9.3249999999999993</v>
       </c>
-      <c r="K4" s="0">
+      <c r="K4">
         <v>0.46566666666666667</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="0">
-        <v>3</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="0">
-        <v>4</v>
-      </c>
-      <c r="G5" s="0">
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
         <v>7.8804984302006531</v>
       </c>
-      <c r="H5" s="0">
+      <c r="H5">
         <v>4.7048852615751064</v>
       </c>
-      <c r="I5" s="0">
+      <c r="I5">
         <v>10.145979669108643</v>
       </c>
-      <c r="J5" s="0">
+      <c r="J5">
         <v>5.6316666666666668</v>
       </c>
-      <c r="K5" s="0">
+      <c r="K5">
         <v>18.335000000000001</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="0">
-        <v>4</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="0">
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="0">
+      <c r="G6">
         <v>4.2349054328967268</v>
       </c>
-      <c r="H6" s="0">
+      <c r="H6">
         <v>3.7400715988091653</v>
       </c>
-      <c r="I6" s="0">
+      <c r="I6">
         <v>4.6986098574673898</v>
       </c>
-      <c r="J6" s="0">
+      <c r="J6">
         <v>7.8836666666666666</v>
       </c>
-      <c r="K6" s="0">
+      <c r="K6">
         <v>15.259333333333332</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="0">
-        <v>4</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="0">
-        <v>4</v>
-      </c>
-      <c r="G7" s="0">
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
         <v>5.0311775008027189</v>
       </c>
-      <c r="H7" s="0">
+      <c r="H7">
         <v>4.0730190227354131</v>
       </c>
-      <c r="I7" s="0">
+      <c r="I7">
         <v>7.2905968662570393</v>
       </c>
-      <c r="J7" s="0">
+      <c r="J7">
         <v>89.263666666666666</v>
       </c>
-      <c r="K7" s="0">
+      <c r="K7">
         <v>17.596666666666668</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="0">
-        <v>4</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="0">
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="0">
+      <c r="G8">
         <v>0.61765981111839807</v>
       </c>
-      <c r="H8" s="0">
+      <c r="H8">
         <v>0.67809762510765048</v>
       </c>
-      <c r="I8" s="0">
+      <c r="I8">
         <v>0.55680402444092236</v>
       </c>
-      <c r="J8" s="0">
+      <c r="J8">
         <v>5.9569999999999999</v>
       </c>
-      <c r="K8" s="0">
+      <c r="K8">
         <v>0.26233333333333336</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9">
         <v>5</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="0">
-        <v>3</v>
-      </c>
-      <c r="G9" s="0">
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
         <v>1.3931728844022728</v>
       </c>
-      <c r="H9" s="0">
+      <c r="H9">
         <v>1.2701243163613307</v>
       </c>
-      <c r="I9" s="0">
+      <c r="I9">
         <v>1.5170437328325523</v>
       </c>
-      <c r="J9" s="0">
+      <c r="J9">
         <v>10.270333333333333</v>
       </c>
-      <c r="K9" s="0">
+      <c r="K9">
         <v>3.4000000000000004</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>3</v>
-      </c>
-      <c r="B10" s="0" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="0">
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="0">
-        <v>3</v>
-      </c>
-      <c r="G10" s="0">
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
         <v>3.5003486645893855</v>
       </c>
-      <c r="H10" s="0">
+      <c r="H10">
         <v>2.6233705176133917</v>
       </c>
-      <c r="I10" s="0">
+      <c r="I10">
         <v>4.2194863405552319</v>
       </c>
-      <c r="J10" s="0">
+      <c r="J10">
         <v>9.1419999999999995</v>
       </c>
-      <c r="K10" s="0">
+      <c r="K10">
         <v>13.606666666666667</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>3</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="0">
-        <v>3</v>
-      </c>
-      <c r="D11" s="0" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="0">
-        <v>4</v>
-      </c>
-      <c r="G11" s="0">
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
         <v>3.2109098696997607</v>
       </c>
-      <c r="H11" s="0">
+      <c r="H11">
         <v>3.3165451656434648</v>
       </c>
-      <c r="I11" s="0">
+      <c r="I11">
         <v>3.1181627829451983</v>
       </c>
-      <c r="J11" s="0">
+      <c r="J11">
         <v>13.994666666666667</v>
       </c>
-      <c r="K11" s="0">
+      <c r="K11">
         <v>22.108000000000001</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>3</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="0">
-        <v>4</v>
-      </c>
-      <c r="D12" s="0" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="0">
+      <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" s="0">
+      <c r="G12">
         <v>6.0178149004880428</v>
       </c>
-      <c r="H12" s="0">
+      <c r="H12">
         <v>6.097439449433935</v>
       </c>
-      <c r="I12" s="0">
+      <c r="I12">
         <v>5.9692283298820845</v>
       </c>
-      <c r="J12" s="0">
+      <c r="J12">
         <v>4.4540000000000006</v>
       </c>
-      <c r="K12" s="0">
+      <c r="K12">
         <v>37.88666666666667</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0">
-        <v>3</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="0">
-        <v>4</v>
-      </c>
-      <c r="D13" s="0" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="0">
+      <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13" s="0">
+      <c r="G13">
         <v>0.62564173456511862</v>
       </c>
-      <c r="H13" s="0">
+      <c r="H13">
         <v>0.76051641723572894</v>
       </c>
-      <c r="I13" s="0">
+      <c r="I13">
         <v>0.45643101496299232</v>
       </c>
-      <c r="J13" s="0">
+      <c r="J13">
         <v>13.827</v>
       </c>
-      <c r="K13" s="0">
-        <v>0.020666666666666667</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0">
-        <v>4</v>
-      </c>
-      <c r="B14" s="0" t="s">
+      <c r="K13">
+        <v>2.0666666666666667E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>1</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="0">
+      <c r="F14">
         <v>2</v>
       </c>
-      <c r="G14" s="0">
+      <c r="G14">
         <v>0.94110655517246666</v>
       </c>
-      <c r="H14" s="0">
+      <c r="H14">
         <v>1.1785115885130653</v>
       </c>
-      <c r="I14" s="0">
+      <c r="I14">
         <v>0.84310233304743198</v>
       </c>
-      <c r="J14" s="0">
+      <c r="J14">
         <v>10.004666666666667</v>
       </c>
-      <c r="K14" s="0">
+      <c r="K14">
         <v>0.78633333333333333</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0">
-        <v>4</v>
-      </c>
-      <c r="B15" s="0" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>1</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="0">
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="G15" s="0">
+      <c r="G15">
         <v>1.507119186048919</v>
       </c>
-      <c r="H15" s="0">
+      <c r="H15">
         <v>1.7711734733880706</v>
       </c>
-      <c r="I15" s="0">
+      <c r="I15">
         <v>1.1968955106556411</v>
       </c>
-      <c r="J15" s="0">
+      <c r="J15">
         <v>17.896000000000001</v>
       </c>
-      <c r="K15" s="0">
+      <c r="K15">
         <v>1.6140000000000001</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0">
-        <v>4</v>
-      </c>
-      <c r="B16" s="0" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>1</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="0">
+      <c r="F16">
         <v>2</v>
       </c>
-      <c r="G16" s="0">
+      <c r="G16">
         <v>0.62644401548616857</v>
       </c>
-      <c r="H16" s="0">
+      <c r="H16">
         <v>1.7489436674727721</v>
       </c>
-      <c r="I16" s="0">
+      <c r="I16">
         <v>1.0212233922411751</v>
       </c>
-      <c r="J16" s="0">
+      <c r="J16">
         <v>69.742999999999995</v>
       </c>
-      <c r="K16" s="0">
+      <c r="K16">
         <v>1.1503333333333334</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0">
-        <v>4</v>
-      </c>
-      <c r="B17" s="0" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17">
         <v>2</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="0">
-        <v>3</v>
-      </c>
-      <c r="G17" s="0">
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
         <v>28.339854634630179</v>
       </c>
-      <c r="H17" s="0">
+      <c r="H17">
         <v>25.354858300166018</v>
       </c>
-      <c r="I17" s="0">
+      <c r="I17">
         <v>31.109035993668744</v>
       </c>
-      <c r="J17" s="0">
+      <c r="J17">
         <v>13.557333333333332</v>
       </c>
-      <c r="K17" s="0">
+      <c r="K17">
         <v>78.149999999999991</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0">
-        <v>4</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="0">
-        <v>3</v>
-      </c>
-      <c r="D18" s="0" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="0">
-        <v>4</v>
-      </c>
-      <c r="G18" s="0">
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
         <v>1.169167877278849</v>
       </c>
-      <c r="H18" s="0">
+      <c r="H18">
         <v>1.3305507789801547</v>
       </c>
-      <c r="I18" s="0">
+      <c r="I18">
         <v>0.98814433613743358</v>
       </c>
-      <c r="J18" s="0">
+      <c r="J18">
         <v>11.056000000000001</v>
       </c>
-      <c r="K18" s="0">
+      <c r="K18">
         <v>1.3639999999999999</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0">
-        <v>4</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="0">
-        <v>3</v>
-      </c>
-      <c r="D19" s="0" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="0">
-        <v>4</v>
-      </c>
-      <c r="G19" s="0">
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
         <v>2.2645498995323279</v>
       </c>
-      <c r="H19" s="0">
+      <c r="H19">
         <v>1.9487353224459802</v>
       </c>
-      <c r="I19" s="0">
+      <c r="I19">
         <v>2.5554722600225883</v>
       </c>
-      <c r="J19" s="0">
+      <c r="J19">
         <v>8.1760000000000002</v>
       </c>
-      <c r="K19" s="0">
+      <c r="K19">
         <v>7.4643333333333342</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0">
-        <v>4</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="0">
-        <v>4</v>
-      </c>
-      <c r="D20" s="0" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="0">
+      <c r="F20">
         <v>1</v>
       </c>
-      <c r="G20" s="0">
+      <c r="G20">
         <v>9.7775451468301231</v>
       </c>
-      <c r="H20" s="0">
+      <c r="H20">
         <v>8.4868752859271446</v>
       </c>
-      <c r="I20" s="0">
+      <c r="I20">
         <v>10.939408963176415</v>
       </c>
-      <c r="J20" s="0">
+      <c r="J20">
         <v>15.619</v>
       </c>
-      <c r="K20" s="0">
+      <c r="K20">
         <v>41.366666666666667</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="0">
-        <v>4</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="0">
-        <v>4</v>
-      </c>
-      <c r="D21" s="0" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="0">
+      <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21" s="0">
+      <c r="G21">
         <v>4.9902633542899064</v>
       </c>
-      <c r="H21" s="0">
+      <c r="H21">
         <v>4.2812881590253946</v>
       </c>
-      <c r="I21" s="0">
+      <c r="I21">
         <v>5.662087655751697</v>
       </c>
-      <c r="J21" s="0">
+      <c r="J21">
         <v>14.076666666666668</v>
       </c>
-      <c r="K21" s="0">
+      <c r="K21">
         <v>27.419</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="0">
-        <v>4</v>
-      </c>
-      <c r="B22" s="0" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>5</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="0">
-        <v>3</v>
-      </c>
-      <c r="G22" s="0">
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
         <v>9.8530860677139067</v>
       </c>
-      <c r="H22" s="0">
+      <c r="H22">
         <v>7.8318318047073605</v>
       </c>
-      <c r="I22" s="0">
+      <c r="I22">
         <v>11.55328882951121</v>
       </c>
-      <c r="J22" s="0">
+      <c r="J22">
         <v>13.388</v>
       </c>
-      <c r="K22" s="0">
+      <c r="K22">
         <v>34.863999999999997</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="0">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>5</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C23">
         <v>1</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="0">
+      <c r="F23">
         <v>2</v>
       </c>
-      <c r="G23" s="0">
+      <c r="G23">
         <v>1.4309307673926377</v>
       </c>
-      <c r="H23" s="0">
+      <c r="H23">
         <v>1.6813176867386692</v>
       </c>
-      <c r="I23" s="0">
+      <c r="I23">
         <v>1.1286372623875647</v>
       </c>
-      <c r="J23" s="0">
+      <c r="J23">
         <v>10.638666666666667</v>
       </c>
-      <c r="K23" s="0">
+      <c r="K23">
         <v>1.9026666666666667</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="0">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>5</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>2</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="0">
-        <v>3</v>
-      </c>
-      <c r="G24" s="0">
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
         <v>57.427268304573168</v>
       </c>
-      <c r="H24" s="0">
+      <c r="H24">
         <v>29.044991658266888</v>
       </c>
-      <c r="I24" s="0">
+      <c r="I24">
         <v>76.151904625512898</v>
       </c>
-      <c r="J24" s="0">
+      <c r="J24">
         <v>7.442333333333333</v>
       </c>
-      <c r="K24" s="0">
+      <c r="K24">
         <v>44.81366666666667</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="0">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>5</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C25">
         <v>2</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="0">
-        <v>3</v>
-      </c>
-      <c r="G25" s="0">
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
         <v>38.413762031089355</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H25">
         <v>20.498144518934389</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I25">
         <v>50.514226364247769</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J25">
         <v>9.1083333333333343</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K25">
         <v>32.214666666666666</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="0">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>5</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="0">
-        <v>3</v>
-      </c>
-      <c r="D26" s="0" t="s">
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="0">
-        <v>4</v>
-      </c>
-      <c r="G26" s="0">
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
         <v>5.6577152210931629</v>
       </c>
-      <c r="H26" s="0">
+      <c r="H26">
         <v>3.6581654358595261</v>
       </c>
-      <c r="I26" s="0">
+      <c r="I26">
         <v>7.1445245491746689</v>
       </c>
-      <c r="J26" s="0">
+      <c r="J26">
         <v>6.9963333333333333</v>
       </c>
-      <c r="K26" s="0">
+      <c r="K26">
         <v>11.813333333333334</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="0">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>5</v>
       </c>
-      <c r="B27" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="0">
-        <v>3</v>
-      </c>
-      <c r="D27" s="0" t="s">
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="0">
-        <v>4</v>
-      </c>
-      <c r="G27" s="0">
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27">
         <v>156.67031430896765</v>
       </c>
-      <c r="H27" s="0">
+      <c r="H27">
         <v>83.217832380615732</v>
       </c>
-      <c r="I27" s="0">
+      <c r="I27">
         <v>205.4546353198638</v>
       </c>
-      <c r="J27" s="0">
+      <c r="J27">
         <v>9.3643333333333327</v>
       </c>
-      <c r="K27" s="0">
+      <c r="K27">
         <v>56.366999999999997</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="0">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>5</v>
       </c>
-      <c r="B28" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="0">
-        <v>3</v>
-      </c>
-      <c r="D28" s="0" t="s">
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" t="s">
         <v>29</v>
       </c>
-      <c r="F28" s="0">
-        <v>4</v>
-      </c>
-      <c r="G28" s="0">
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
         <v>49.880459175509799</v>
       </c>
-      <c r="H28" s="0">
+      <c r="H28">
         <v>25.742837255264842</v>
       </c>
-      <c r="I28" s="0">
+      <c r="I28">
         <v>65.912861150450567</v>
       </c>
-      <c r="J28" s="0">
+      <c r="J28">
         <v>7.4050000000000002</v>
       </c>
-      <c r="K28" s="0">
+      <c r="K28">
         <v>38.585333333333331</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="0">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>5</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="0">
-        <v>4</v>
-      </c>
-      <c r="D29" s="0" t="s">
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="0">
-        <v>4</v>
-      </c>
-      <c r="G29" s="0">
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29">
         <v>6.4250851470491881</v>
       </c>
-      <c r="H29" s="0">
+      <c r="H29">
         <v>4.1532850350478183</v>
       </c>
-      <c r="I29" s="0">
+      <c r="I29">
         <v>8.1194192240492775</v>
       </c>
-      <c r="J29" s="0">
+      <c r="J29">
         <v>6.8546666666666676</v>
       </c>
-      <c r="K29" s="0">
+      <c r="K29">
         <v>12.703333333333333</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="0">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>5</v>
       </c>
-      <c r="B30" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="0">
-        <v>4</v>
-      </c>
-      <c r="D30" s="0" t="s">
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="0">
+      <c r="F30">
         <v>1</v>
       </c>
-      <c r="G30" s="0">
+      <c r="G30">
         <v>2.6803072891361914</v>
       </c>
-      <c r="H30" s="0">
+      <c r="H30">
         <v>2.3847007284654338</v>
       </c>
-      <c r="I30" s="0">
+      <c r="I30">
         <v>2.9664635363089626</v>
       </c>
-      <c r="J30" s="0">
+      <c r="J30">
         <v>7.5493333333333332</v>
       </c>
-      <c r="K30" s="0">
+      <c r="K30">
         <v>7.5403333333333338</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="0">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>6</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C31">
         <v>1</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="0">
+      <c r="F31">
         <v>2</v>
       </c>
-      <c r="G31" s="0">
+      <c r="G31">
         <v>11.76749128587363</v>
       </c>
-      <c r="H31" s="0">
+      <c r="H31">
         <v>9.3099572274973212</v>
       </c>
-      <c r="I31" s="0">
+      <c r="I31">
         <v>13.885432019550256</v>
       </c>
-      <c r="J31" s="0">
+      <c r="J31">
         <v>15.700333333333333</v>
       </c>
-      <c r="K31" s="0">
+      <c r="K31">
         <v>36.840000000000003</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="0">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32">
         <v>6</v>
       </c>
-      <c r="B32" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="0">
-        <v>3</v>
-      </c>
-      <c r="D32" s="0" t="s">
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="0">
-        <v>4</v>
-      </c>
-      <c r="G32" s="0">
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32">
         <v>3.5028743970847893</v>
       </c>
-      <c r="H32" s="0">
+      <c r="H32">
         <v>4.1689622771732058</v>
       </c>
-      <c r="I32" s="0">
+      <c r="I32">
         <v>2.7144987384151875</v>
       </c>
-      <c r="J32" s="0">
+      <c r="J32">
         <v>15.401666666666666</v>
       </c>
-      <c r="K32" s="0">
+      <c r="K32">
         <v>28.981333333333332</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="0">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>6</v>
       </c>
-      <c r="B33" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="0">
-        <v>3</v>
-      </c>
-      <c r="D33" s="0" t="s">
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="0">
-        <v>4</v>
-      </c>
-      <c r="G33" s="0">
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33">
         <v>111.28056033499099</v>
       </c>
-      <c r="H33" s="0">
+      <c r="H33">
         <v>60.554468053821289</v>
       </c>
-      <c r="I33" s="0">
+      <c r="I33">
         <v>145.92705954389714</v>
       </c>
-      <c r="J33" s="0">
+      <c r="J33">
         <v>7.6306666666666665</v>
       </c>
-      <c r="K33" s="0">
+      <c r="K33">
         <v>70.528666666666666</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="0">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34">
         <v>6</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="0">
-        <v>4</v>
-      </c>
-      <c r="D34" s="0" t="s">
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="0">
-        <v>4</v>
-      </c>
-      <c r="G34" s="0">
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34">
         <v>1.3279469696564949</v>
       </c>
-      <c r="H34" s="0">
+      <c r="H34">
         <v>1.8854589130358157</v>
       </c>
-      <c r="I34" s="0">
+      <c r="I34">
         <v>0.97886812220553232</v>
       </c>
-      <c r="J34" s="0">
+      <c r="J34">
         <v>61.921666666666667</v>
       </c>
-      <c r="K34" s="0">
+      <c r="K34">
         <v>0.26566666666666666</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="0">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35">
         <v>6</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="0">
-        <v>4</v>
-      </c>
-      <c r="D35" s="0" t="s">
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
         <v>16</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" t="s">
         <v>29</v>
       </c>
-      <c r="F35" s="0">
-        <v>4</v>
-      </c>
-      <c r="G35" s="0">
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35">
         <v>1.1353434069885373</v>
       </c>
-      <c r="H35" s="0">
+      <c r="H35">
         <v>1.4318774340669977</v>
       </c>
-      <c r="I35" s="0">
+      <c r="I35">
         <v>0.74095098561597084</v>
       </c>
-      <c r="J35" s="0">
+      <c r="J35">
         <v>19.012</v>
       </c>
-      <c r="K35" s="0">
-        <v>0.025999999999999999</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0">
+      <c r="K35">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>6</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C36" s="0">
-        <v>4</v>
-      </c>
-      <c r="D36" s="0" t="s">
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="0">
+      <c r="F36">
         <v>1</v>
       </c>
-      <c r="G36" s="0">
+      <c r="G36">
         <v>7.1185230954673324</v>
       </c>
-      <c r="H36" s="0">
+      <c r="H36">
         <v>4.5615443852636872</v>
       </c>
-      <c r="I36" s="0">
+      <c r="I36">
         <v>9.0115544366915383</v>
       </c>
-      <c r="J36" s="0">
+      <c r="J36">
         <v>7.4016666666666664</v>
       </c>
-      <c r="K36" s="0">
+      <c r="K36">
         <v>15.237333333333334</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="0">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37">
         <v>6</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="0">
+      <c r="C37">
         <v>5</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="0">
-        <v>3</v>
-      </c>
-      <c r="G37" s="0">
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37">
         <v>6.776796855638934</v>
       </c>
-      <c r="H37" s="0">
+      <c r="H37">
         <v>4.6106555844012345</v>
       </c>
-      <c r="I37" s="0">
+      <c r="I37">
         <v>8.4365300095803182</v>
       </c>
-      <c r="J37" s="0">
+      <c r="J37">
         <v>6.8836666666666675</v>
       </c>
-      <c r="K37" s="0">
+      <c r="K37">
         <v>17.604333333333333</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="0">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A38">
         <v>6</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="0">
+      <c r="C38">
         <v>5</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" t="s">
         <v>24</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" t="s">
         <v>28</v>
       </c>
-      <c r="F38" s="0">
-        <v>3</v>
-      </c>
-      <c r="G38" s="0">
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38">
         <v>3.4099527469765047</v>
       </c>
-      <c r="H38" s="0">
+      <c r="H38">
         <v>3.1085935052157296</v>
       </c>
-      <c r="I38" s="0">
+      <c r="I38">
         <v>3.7050613183415124</v>
       </c>
-      <c r="J38" s="0">
+      <c r="J38">
         <v>10.526666666666666</v>
       </c>
-      <c r="K38" s="0">
+      <c r="K38">
         <v>14.638333333333334</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="0">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39">
         <v>6</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="0">
+      <c r="C39">
         <v>5</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" t="s">
         <v>28</v>
       </c>
-      <c r="F39" s="0">
-        <v>3</v>
-      </c>
-      <c r="G39" s="0">
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39">
         <v>22.521289805136721</v>
       </c>
-      <c r="H39" s="0">
+      <c r="H39">
         <v>15.437646991073336</v>
       </c>
-      <c r="I39" s="0">
+      <c r="I39">
         <v>27.943023484158449</v>
       </c>
-      <c r="J39" s="0">
+      <c r="J39">
         <v>10.676333333333334</v>
       </c>
-      <c r="K39" s="0">
+      <c r="K39">
         <v>41.317666666666668</v>
       </c>
     </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H40">
+        <f>AVERAGE(H2:H39)</f>
+        <v>9.5635039583759216</v>
+      </c>
+      <c r="K40">
+        <f>AVERAGE(K2:K39)</f>
+        <v>20.400649122807021</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>